--- a/red_book/excel/笔记列表明细表-20260829.xlsx
+++ b/red_book/excel/笔记列表明细表-20260829.xlsx
@@ -267,7 +267,7 @@
         <v>4031.0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1306.0</v>
+        <v>1311.0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.077</v>
@@ -502,7 +502,7 @@
         <v>13496.0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2058.0</v>
+        <v>2062.0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.151</v>
@@ -643,7 +643,7 @@
         <v>19747.0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1988.0</v>
+        <v>1994.0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.1</v>
